--- a/TESTS/zlit_7_kholms.xlsx
+++ b/TESTS/zlit_7_kholms.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Артур Конан Дойл — британський письменник лікар що створив найвідомішого детектива всіх часів</t>
+          <t>Артур Конан Дойл</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -645,6 +655,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Дедукцією — логічним висновком від загального до конкретного на основі уважного спостереження деталей</t>
+          <t>Дедукцією</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -729,6 +749,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Звернув увагу на деталі — заглушений вентиляційний отвір мотузку і дзвінок — і встановив схему злочину</t>
+          <t>Звернув увагу на деталі</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Доктор Ройлотт — вітчим жертви; мотив — спадщина яку він втрачав би при її одруженні</t>
+          <t>Доктор Ройлотт</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>У несподіваній оригінальності — щоб пограбувати банк злочинці придумали абсурдну організацію яка відволікла жертву</t>
+          <t>У несподіваній оригінальності</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>У якому місті відбуваються всі пригоди Шерлока Холмса?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Едінбург</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Лондон — туманне вікторіанське місто кінця XIX ст.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Манчестер</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бірмінгем</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Яка особлива здатність Холмса щодо людей при першій зустрічі?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він читає думки</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Помічаючи деталі одягу, постави, рук і поведінки, він може зробити точні висновки про фах, звички і характер людини</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він гіпнотизує</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він завжди знає ім'я людини</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Яким є стиль оповіді у більшості пригод Холмса?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Від третьої особи</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Від першої особи Ватсона, що бачить усе очима звичайної людини і разом із читачем дивується геніальності Холмса</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Від першої особи Холмса</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Від автора</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Звідки прийшла до Холмса Гелен Стоунер і чого вона побоювалась?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>З країни</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З лондонської вулиці, бо боялась, що вітчим доктор Ройлотт збирається вбити її, як він вбив її сестру</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Від поліції</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Від сусіда</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що сталося зі сестрою Гелен — Джулією — перед смертю?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона заснула і не прокинулась</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона вмерла за загадкових обставин: вночі почувся її крик, і вона встигла лише сказати про «пістру стрічку»</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона захворіла</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона просто поїхала</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Як Холмс і Ватсон проникли до будинку, щоб розгадати таємницю смерті Джулії?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Через парадні двері вдень</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вночі непомітно потрапили до кімнати Гелен і чекали у темряві</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Попросили Гелен відчинити</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Через вікно вдень</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Що насправді виявилось «пістрою стрічкою», яку сестра Гелен встигла назвати перед смертю?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Шаль</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Отруйна болотяна гадюка — рідкісна і смертоносна змія, яку натренував Ройлотт</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Стрічка у волоссі</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сліди крові</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як Ройлотт переганяв змію до кімнати жертви?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Через двері</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Крізь вентиляційний отвір між кімнатами — змія лізла по шнуру від ліжка</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Підкладав у ліжко вдень</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Через вікно</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Яка іронічна справедливість чекала на Ройлотта у фіналі «Пістрої стрічки»?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його заарештувала поліція</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він сам загинув від отруйного укусу змії, яку Холмс, ударивши по шнуру, відіслав назад</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він утік з країни</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він здався добровільно</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що таке «Спілка рудих» і чому вона привернула увагу заможного рудого торговця Вілсона?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Справжня благодійна організація</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Оголошення обіцяло рудоволосим чоловікам чудовий заробіток за переписування тексту — і Вілсон щодня ходив туди</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Клуб за інтересами</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поліцейська структура</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Де фізично Вілсон виконував роботу для «Спілки», поки тривала схема?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>На вулиці</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У спеціально відведеному офісі, куди він приходив щодня і переписував рядки тексту</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У своїй крамниці</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вдома</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Чому схему «Спілки рудих» зрештою раптово ліквідували?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони заробили достатньо грошей</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Злочинці завершили рити тунель під банком — Спілка більше не потрібна була для відволікання Вілсона</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Їх викрила поліція першими</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вілсон сам відмовився</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Яку ключову деталь Холмс помітив у самому Вілсоні, що навів його на рішення?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Брудні руки</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Мозолі та знебарвленість на правій руці, що свідчили про тривалу ручну роботу в підвалі</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Незвичайний одяг</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Запах фарби</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Де Холмс і поліція влаштували засідку для злочинців у «Спілці рудих»?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В офісі Спілки</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У підвалі банку, куди вів тунель, прорий злочинцями</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>На вулиці біля банку</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У крамниці Вілсона</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Хто виявився організатором схеми «Спілки рудих»?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Випадковий злодій</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Джон Клей — хитрий і небезпечний злочинець-джентльмен, один з найрозшукуваніших в Англії</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Помічник Вілсона</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Банківський клерк</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що об'єднує «Пістру стрічку» і «Спілку рудих» як детективні оповідання?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Однаковий злочинець</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидва побудовані на незвичайному задумі, де ключ до розгадки — помічена Холмсом дрібна деталь</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Однакова жертва</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Однакова кількість підозрюваних</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Яку роль відіграє Лондон як місто у атмосфері оповідань про Холмса?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише фон</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Туманний, темний, густонаселений Лондон кінця XIX ст. є органічним середовищем детективної таємниці</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Місто завжди позитивне</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лондон як тло не описується</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Чим детективна проза Конан Дойла відрізнялась від більш ранніх детективів, таких як По?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічим особливим</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Холмс вирішує справи виключно логічним аналізом фактів, без везіння і надприродного, — з можливістю читача слідкувати за думкою</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Конан Дойл писав коротше</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Конан Дойл не любив детективів</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Яким, попри геніальність, є Холмс у стосунках з людьми?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Теплим і сердечним</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Холодним і відстороненим — він аналізує людей, а не любить їх, що часом відштовхує</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Завжди ввічливим</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дуже емоційним</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Яку функцію виконує образ Ватсона для читача?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ватсон лише записує</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ватсон — «нормальна» людина, поруч з якою читач переживає здивування і поступово розуміє хід думок Холмса</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ватсон зрозуміліший за Холмса</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ватсон і є головний герой</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чому Шерлок Холмс став культурним символом, що пережив свого автора і свою епоху?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо про нього знято фільми</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо він втілює ідеал торжества розуму над злом і хаосом — мрію про справедливість через інтелект</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо він красивий персонаж</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо Конан Дойл добре рекламував книги</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Чим метод Холмса відрізняється від методу поліції в оповіданнях?</t>
+          <t>Холмс вирішує справи дедукцією — побудовою логічного ланцюга від спостережених фактів до єдиного можливого висновку.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє Лондон у атмосфері оповідань про Холмса?</t>
+          <t>Туманний вікторіанський Лондон є не просто фоном, а органічним середовищем детективної таємниці у оповіданнях.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Чому оповідання про Холмса вважаються класикою жанру?</t>
+          <t>Оповідання Конан Дойла вважаються класикою детективу, бо ввели логічний аналіз як основний інструмент розкриття злочину.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея оповідань Конан Дойла?</t>
+          <t>Головна ідея оповідань Конан Дойла — розум і спостережливість можуть перемогти навіть найхитріший злочин.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Що символізує образ Холмса для культури?</t>
+          <t>Образ Холмса у світовій культурі став символом логіки та інтелектуальної незалежності.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що таке «детективна проза» і яку роль відіграв Конан Дойл у її розвитку?</t>
+          <t>Конан Дойл першим вигадав детективну прозу як жанр, до нього не існувало жодних детективних творів.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які риси роблять Шерлока Холмса геніальним детективом?</t>
+          <t>Що відбулось у двох оповіданнях про Холмса?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Гострий аналітичний розум</t>
+          <t>Ройлотт загинув від власної отруйної змії</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Увага до незначних деталей</t>
+          <t>Злочинці «Спілки рудих» були спіймані в тунелі під банком</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Використання фізичної сили</t>
+          <t>Холмс помилився у висновках</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Презирство до шаблонного мислення</t>
+          <t>Ватсон самостійно розкрив злочин</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Звернув увагу на мозолі на руках Вілсона колір його штанів і зв'язав це з роботою в підвалі — і все зійшлось</t>
+          <t>Звернув увагу на мозолі на руках Вілсона колір його штанів і зв'язав це з роботою в підвалі</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2337,6 +2539,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Оповідача і читацького «дзеркала» — він як ми не розуміє всього одразу але чесно описує геній Холмса</t>
+          <t>Оповідача і читацького «дзеркала»</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
